--- a/TTRPG_Market_Analysis_Phmurt.xlsx
+++ b/TTRPG_Market_Analysis_Phmurt.xlsx
@@ -10,6 +10,8 @@
   <sheets>
     <sheet name="Competitor Analysis" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Phmurt Studios Forecast" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Harsh Reality Model" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Odds of Success" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="401">
   <si>
     <t xml:space="preserve">D&amp;D / TTRPG Tool Market — Competitor Analysis</t>
   </si>
@@ -744,19 +746,501 @@
   </si>
   <si>
     <t xml:space="preserve">All-in-one platform, partnerships, brand deals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phmurt Studios — Harsh Reality Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pessimistic assumptions. No wishful thinking. What actually happens to most indie tool sites.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARSH ASSUMPTIONS — Why each number is lower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harsh Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs. Base Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reality Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting Monthly Visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs 5,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You're brand new. Nobody knows you exist. Most sites start at &lt;500.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs 12%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6% is still good. Most indie sites grow 2-5%. SEO takes 6-12 months to kick in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth Decay Rate (per year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs 40%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth slows fast. By year 3 you're fighting for scraps of organic traffic.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free-to-Paid Conversion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs 2.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2% is realistic. Most freemium tools see 1-3%. D&amp;D players are notoriously cheap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Subscription ($/month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs $5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You'll need to undercut established competitors to win users.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party Plan ($/month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs $10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group plans need to feel like a deal or nobody bothers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lifetime License ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs $50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lower to drive early adoption. Lifetime buyers often never come back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro % of Paid Users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs 60%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">More people choose the cheapest option when they're unsure about you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party % of Paid Users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs 25%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group coordination is hard. Most DMs just buy solo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs 15%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Higher lifetime % = less recurring revenue. One-time buyers are a trap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly Churn (Pro)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs 8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12% monthly churn = 78% annual. Most users try it for 1-2 months and leave.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly Churn (Party)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs 5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groups are stickier but campaigns end. When the campaign dies, the sub dies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs $3.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPG niche CPMs are low. You're not a mainstream site. Adblockers kill 30-40%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pages Per Visit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most visitors hit one generator and leave. Bounce rates for tool sites are 60%+.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Server Costs ($/month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheaper to start, but this WILL spike if you get any real traffic.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Server Cost Growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3% monthly. For a static site with &lt;5K visitors, hosting is basically flat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing ($/month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs $200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You're indie. You're doing this on a shoestring.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your Time (hours/week)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is the hidden cost. 20 hrs/week of unpaid dev time = ~$50K/yr opportunity cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opportunity Cost ($/year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What you'd earn spending those 20 hrs/week at a normal job. THIS IS A REAL COST.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as base model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-YEAR HARSH FORECAST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Cash Expenses ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash Profit (before your time) ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your Time (opportunity cost) ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE Net Profit (Loss) ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit Margin (incl. time) (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective Hourly Rate ($/hr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative Cash Revenue ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative TRUE Profit (Loss) ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probability Analysis — Will This Actually Work?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Based on indie dev survival rates, TTRPG tool market data, and comparable outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUTCOME PROBABILITIES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outcome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What This Looks Like</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abandoned (year 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You burn out, lose motivation, or life gets in the way. Most common outcome for solo devs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hobby Project Forever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0–$500/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site exists, gets some traffic, but you never monetize it. It's a portfolio piece, not a business.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$500–$5K/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small Patreon, some ad revenue. Covers hosting + a nice dinner each month. Comparable: RPG Tinker, Watabou.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$5K–$50K/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meaningful money but not life-changing. You keep your day job. Comparable: Improved Initiative, Chartopia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serious Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enough to consider going full-time. Comparable: Kassoon, Owlbear Rodeo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$200K–$1M/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full-time income for a small team. Comparable: Dungeon Fog, Inkarnate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breakout Success</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You become a known name in the space. Comparable: Early Foundry VTT, TaleSpire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KEY RISK FACTORS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likelihood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why It Matters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D&amp;D Beyond moat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIGH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wizards of the Coast owns the official tools. They can undercut anyone on features.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo dev burnout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRITICAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building AND maintaining a full-stack app alone is brutal. Features rot without updates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEO is a marathon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google takes 6-18 months to rank new sites. You'll get almost zero organic traffic at first.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free alternatives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5e.tools, donjon, Kobold Plus are all free. Hard to charge for what others give away.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OGL / License risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEDIUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hasbro's OGL drama showed they can change the rules. Your content could become illegal overnight.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market saturation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every D&amp;D dev is building tools. The space is crowded with passionate hobbyists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conversion wall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D&amp;D players use tons of free tools. Getting them to pay for another one is really hard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feature creep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You already have character builder, campaign mgr, generators, maps. Each one needs maintenance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile gap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lots of D&amp;D play happens at tables with phones. If your site isn't mobile-perfect, you lose users.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI disruption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChatGPT can generate NPCs, encounters, loot. Your generators compete with a free AI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHAT ACTUALLY MOVES THE NEEDLE (to beat the odds)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difficulty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hit Reddit/YouTube virality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One front-page Reddit post or popular YouTuber mention can 50x your traffic overnight. Can't plan for it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEO-optimized generators</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"D&amp;D NPC generator" gets 12K searches/month. Rank #1 for 5-10 of these and you have consistent traffic.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community &amp; Discord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Discord with 1000+ members creates organic word-of-mouth. This is how Owlbear Rodeo grew.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unique feature nobody else has</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign manager + generators + combat in one place is rare. Lean into the all-in-one angle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Content creator partnerships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get D&amp;D YouTubers and podcasters to use your tools on stream. Social proof is everything.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile-first experience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most D&amp;D tools are desktop-only. A great mobile experience is a real differentiator.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patreon before subscriptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EASY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patreon has built-in discovery. Easier to get $3/patron than build your own payment system.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ship fast, ship often</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release a new generator or feature every 2 weeks. Momentum = retention. Stale sites die.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE BOTTOM LINE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There's roughly an 80% chance this stays a hobby project earning less than $5K/year.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There's roughly a 20% chance it becomes meaningful income ($5K+/year).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There's roughly an 8% chance it becomes serious money ($50K+/year).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There's roughly a 2% chance it becomes a real business ($200K+/year).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The MOST LIKELY outcome: you build something cool, get 5-20K monthly visitors, make a few hundred bucks a month from ads and a small Patreon, and it's a great portfolio piece / passion project that doesn't pay for itself in terms of your time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That said — your site already has more features than most indie tools. The combination of generators + campaign manager + character builder + combat system is genuinely rare. Most competitors only do ONE of those things. If you can nail the SEO game and build a community, you're in the 12% tier at minimum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best realistic target: $500-$2,000/month within 18 months through Patreon + ads. That's achievable and puts you ahead of 90% of indie D&amp;D tool devs.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="\$#,##0"/>
+    <numFmt numFmtId="168" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
+    <numFmt numFmtId="169" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -873,8 +1357,156 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FFEF4444"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="11"/>
+      <color rgb="FF9999AA"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FFEF4444"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFF59E0B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFEF4444"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFF59E0B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFEF4444"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FFF59E0B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FFF59E0B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FFF2E8D6"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF60A5FA"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF4ADE80"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFF2E8D6"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FFC9A84C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFF2E8D6"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF9999AA"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="11"/>
+      <color rgb="FFF59E0B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4ADE80"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFC9A84C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -911,6 +1543,24 @@
         <bgColor rgb="FF1A1A2E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A0F0F"/>
+        <bgColor rgb="FF1A0A0A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A0A0A"/>
+        <bgColor rgb="FF1A0F0F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0A1A0A"/>
+        <bgColor rgb="FF0F0F23"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
@@ -961,7 +1611,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="71">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1088,6 +1738,162 @@
     </xf>
     <xf numFmtId="167" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1109,19 +1915,19 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF1A0A0A"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF0F0F23"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFC9A84C"/>
       <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF60A5FA"/>
       <rgbColor rgb="FFD4433A"/>
       <rgbColor rgb="FFF2E8D6"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FF1A0F0F"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFCCCCFF"/>
@@ -1145,17 +1951,17 @@
       <rgbColor rgb="FF4ADE80"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFC9A84C"/>
-      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FFF59E0B"/>
+      <rgbColor rgb="FFEF4444"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF9999AA"/>
       <rgbColor rgb="FF16213E"/>
       <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF1A1A2E"/>
+      <rgbColor rgb="FF0A1A0A"/>
       <rgbColor rgb="FF2D1F3D"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF1A1A2E"/>
       <rgbColor rgb="FF2A2A44"/>
     </indexedColors>
   </colors>
@@ -3554,4 +4360,2152 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FFEF4444"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G90"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+    </row>
+    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B6" s="35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>248</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>250</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>262</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>265</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>271</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B15" s="16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="B16" s="16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="B17" s="16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>281</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="B19" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>284</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>265</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="B21" s="16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="B22" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C22" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+    </row>
+    <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="B24" s="35" t="n">
+        <v>52000</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B25" s="35" t="n">
+        <v>150</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+    </row>
+    <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="G29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="B30" s="18" t="n">
+        <f aca="false">ROUND(B6*(1+B7)^12,0)</f>
+        <v>2012</v>
+      </c>
+      <c r="C30" s="18" t="n">
+        <f aca="false">ROUND(B30*(1+B7*(1-B8)^1)^12,0)</f>
+        <v>2869</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <f aca="false">ROUND(C30*(1+B7*(1-B8)^2)^12,0)</f>
+        <v>3430</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <f aca="false">ROUND(D30*(1+B7*(1-B8)^3)^12,0)</f>
+        <v>3752</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <f aca="false">ROUND(E30*(1+B7*(1-B8)^4)^12,0)</f>
+        <v>3924</v>
+      </c>
+      <c r="G30" s="4"/>
+    </row>
+    <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="B31" s="19" t="n">
+        <f aca="false">ROUND((B6+B30)/2*12*0.6,0)</f>
+        <v>10843</v>
+      </c>
+      <c r="C31" s="19" t="n">
+        <f aca="false">ROUND((B30+C30)/2*12*0.6,0)</f>
+        <v>17572</v>
+      </c>
+      <c r="D31" s="19" t="n">
+        <f aca="false">ROUND((C30+D30)/2*12*0.6,0)</f>
+        <v>22676</v>
+      </c>
+      <c r="E31" s="19" t="n">
+        <f aca="false">ROUND((D30+E30)/2*12*0.6,0)</f>
+        <v>25855</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <f aca="false">ROUND((E30+F30)/2*12*0.6,0)</f>
+        <v>27634</v>
+      </c>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B32" s="18" t="n">
+        <f aca="false">ROUND(B31*B9,0)</f>
+        <v>130</v>
+      </c>
+      <c r="C32" s="18" t="n">
+        <f aca="false">ROUND(C31*B9,0)</f>
+        <v>211</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <f aca="false">ROUND(D31*B9,0)</f>
+        <v>272</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <f aca="false">ROUND(E31*B9,0)</f>
+        <v>310</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <f aca="false">ROUND(F31*B9,0)</f>
+        <v>332</v>
+      </c>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="B33" s="19" t="n">
+        <f aca="false">ROUND(B32*B13*(1/(1+B16))*0.5,0)</f>
+        <v>32</v>
+      </c>
+      <c r="C33" s="19" t="n">
+        <f aca="false">ROUND(B33*(1-B16)^12+C32*B13*(1/(1+B16))*0.5,0)</f>
+        <v>59</v>
+      </c>
+      <c r="D33" s="19" t="n">
+        <f aca="false">ROUND(C33*(1-B16)^12+D32*B13*(1/(1+B16))*0.5,0)</f>
+        <v>80</v>
+      </c>
+      <c r="E33" s="19" t="n">
+        <f aca="false">ROUND(D33*(1-B16)^12+E32*B13*(1/(1+B16))*0.5,0)</f>
+        <v>93</v>
+      </c>
+      <c r="F33" s="19" t="n">
+        <f aca="false">ROUND(E33*(1-B16)^12+F32*B13*(1/(1+B16))*0.5,0)</f>
+        <v>102</v>
+      </c>
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="B34" s="18" t="n">
+        <f aca="false">ROUND(B32*B14*(1/(1+B17))*0.5,0)</f>
+        <v>12</v>
+      </c>
+      <c r="C34" s="18" t="n">
+        <f aca="false">ROUND(B34*(1-B17)^12+C32*B14*(1/(1+B17))*0.5,0)</f>
+        <v>24</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <f aca="false">ROUND(C34*(1-B17)^12+D32*B14*(1/(1+B17))*0.5,0)</f>
+        <v>34</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <f aca="false">ROUND(D34*(1-B17)^12+E32*B14*(1/(1+B17))*0.5,0)</f>
+        <v>41</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <f aca="false">ROUND(E34*(1-B17)^12+F32*B14*(1/(1+B17))*0.5,0)</f>
+        <v>46</v>
+      </c>
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="B35" s="19" t="n">
+        <f aca="false">ROUND(B32*B15,0)</f>
+        <v>33</v>
+      </c>
+      <c r="C35" s="19" t="n">
+        <f aca="false">ROUND(C32*B15,0)</f>
+        <v>53</v>
+      </c>
+      <c r="D35" s="19" t="n">
+        <f aca="false">ROUND(D32*B15,0)</f>
+        <v>68</v>
+      </c>
+      <c r="E35" s="19" t="n">
+        <f aca="false">ROUND(E32*B15,0)</f>
+        <v>78</v>
+      </c>
+      <c r="F35" s="19" t="n">
+        <f aca="false">ROUND(F32*B15,0)</f>
+        <v>83</v>
+      </c>
+      <c r="G35" s="4"/>
+    </row>
+    <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="15"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="B37" s="38" t="n">
+        <f aca="false">B33*B10*12+B34*B11*12</f>
+        <v>2688</v>
+      </c>
+      <c r="C37" s="38" t="n">
+        <f aca="false">C33*B10*12+C34*B11*12</f>
+        <v>5136</v>
+      </c>
+      <c r="D37" s="38" t="n">
+        <f aca="false">D33*B10*12+D34*B11*12</f>
+        <v>7104</v>
+      </c>
+      <c r="E37" s="38" t="n">
+        <f aca="false">E33*B10*12+E34*B11*12</f>
+        <v>8400</v>
+      </c>
+      <c r="F37" s="38" t="n">
+        <f aca="false">F33*B10*12+F34*B11*12</f>
+        <v>9312</v>
+      </c>
+      <c r="G37" s="4"/>
+    </row>
+    <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="B38" s="39" t="n">
+        <f aca="false">B35*B12</f>
+        <v>1320</v>
+      </c>
+      <c r="C38" s="39" t="n">
+        <f aca="false">C35*B12</f>
+        <v>2120</v>
+      </c>
+      <c r="D38" s="39" t="n">
+        <f aca="false">D35*B12</f>
+        <v>2720</v>
+      </c>
+      <c r="E38" s="39" t="n">
+        <f aca="false">E35*B12</f>
+        <v>3120</v>
+      </c>
+      <c r="F38" s="39" t="n">
+        <f aca="false">F35*B12</f>
+        <v>3320</v>
+      </c>
+      <c r="G38" s="4"/>
+    </row>
+    <row r="39" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="B39" s="38" t="n">
+        <f aca="false">ROUND(B31*B19*B18/1000,0)</f>
+        <v>65</v>
+      </c>
+      <c r="C39" s="38" t="n">
+        <f aca="false">ROUND(C31*B19*B18/1000,0)</f>
+        <v>105</v>
+      </c>
+      <c r="D39" s="38" t="n">
+        <f aca="false">ROUND(D31*B19*B18/1000,0)</f>
+        <v>136</v>
+      </c>
+      <c r="E39" s="38" t="n">
+        <f aca="false">ROUND(E31*B19*B18/1000,0)</f>
+        <v>155</v>
+      </c>
+      <c r="F39" s="38" t="n">
+        <f aca="false">ROUND(F31*B19*B18/1000,0)</f>
+        <v>166</v>
+      </c>
+      <c r="G39" s="4"/>
+    </row>
+    <row r="40" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B40" s="40" t="n">
+        <f aca="false">B37+B38+B39</f>
+        <v>4073</v>
+      </c>
+      <c r="C40" s="40" t="n">
+        <f aca="false">C37+C38+C39</f>
+        <v>7361</v>
+      </c>
+      <c r="D40" s="40" t="n">
+        <f aca="false">D37+D38+D39</f>
+        <v>9960</v>
+      </c>
+      <c r="E40" s="40" t="n">
+        <f aca="false">E37+E38+E39</f>
+        <v>11675</v>
+      </c>
+      <c r="F40" s="40" t="n">
+        <f aca="false">F37+F38+F39</f>
+        <v>12798</v>
+      </c>
+      <c r="G40" s="4"/>
+    </row>
+    <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="17"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="4"/>
+    </row>
+    <row r="42" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B42" s="39" t="n">
+        <f aca="false">ROUND(B20*12*(1+B21)^6,0)</f>
+        <v>430</v>
+      </c>
+      <c r="C42" s="39" t="n">
+        <f aca="false">ROUND(B42*(1+B21)^12,0)</f>
+        <v>613</v>
+      </c>
+      <c r="D42" s="39" t="n">
+        <f aca="false">ROUND(C42*(1+B21)^12,0)</f>
+        <v>874</v>
+      </c>
+      <c r="E42" s="39" t="n">
+        <f aca="false">ROUND(D42*(1+B21)^12,0)</f>
+        <v>1246</v>
+      </c>
+      <c r="F42" s="39" t="n">
+        <f aca="false">ROUND(E42*(1+B21)^12,0)</f>
+        <v>1776</v>
+      </c>
+      <c r="G42" s="4"/>
+    </row>
+    <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="B43" s="38" t="n">
+        <f aca="false">B22*12</f>
+        <v>1200</v>
+      </c>
+      <c r="C43" s="38" t="n">
+        <f aca="false">B22*12</f>
+        <v>1200</v>
+      </c>
+      <c r="D43" s="38" t="n">
+        <f aca="false">B22*12</f>
+        <v>1200</v>
+      </c>
+      <c r="E43" s="38" t="n">
+        <f aca="false">B22*12</f>
+        <v>1200</v>
+      </c>
+      <c r="F43" s="38" t="n">
+        <f aca="false">B22*12</f>
+        <v>1200</v>
+      </c>
+      <c r="G43" s="4"/>
+    </row>
+    <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B44" s="39" t="n">
+        <f aca="false">B25</f>
+        <v>150</v>
+      </c>
+      <c r="C44" s="39" t="n">
+        <f aca="false">B25</f>
+        <v>150</v>
+      </c>
+      <c r="D44" s="39" t="n">
+        <f aca="false">B25</f>
+        <v>150</v>
+      </c>
+      <c r="E44" s="39" t="n">
+        <f aca="false">B25</f>
+        <v>150</v>
+      </c>
+      <c r="F44" s="39" t="n">
+        <f aca="false">B25</f>
+        <v>150</v>
+      </c>
+      <c r="G44" s="4"/>
+    </row>
+    <row r="45" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B45" s="38" t="n">
+        <f aca="false">ROUND((B37+B38)*0.035,0)</f>
+        <v>140</v>
+      </c>
+      <c r="C45" s="38" t="n">
+        <f aca="false">ROUND((C37+C38)*0.035,0)</f>
+        <v>254</v>
+      </c>
+      <c r="D45" s="38" t="n">
+        <f aca="false">ROUND((D37+D38)*0.035,0)</f>
+        <v>344</v>
+      </c>
+      <c r="E45" s="38" t="n">
+        <f aca="false">ROUND((E37+E38)*0.035,0)</f>
+        <v>403</v>
+      </c>
+      <c r="F45" s="38" t="n">
+        <f aca="false">ROUND((F37+F38)*0.035,0)</f>
+        <v>442</v>
+      </c>
+      <c r="G45" s="4"/>
+    </row>
+    <row r="46" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="B46" s="41" t="n">
+        <f aca="false">B42+B43+B44+B45</f>
+        <v>1920</v>
+      </c>
+      <c r="C46" s="41" t="n">
+        <f aca="false">C42+C43+C44+C45</f>
+        <v>2217</v>
+      </c>
+      <c r="D46" s="41" t="n">
+        <f aca="false">D42+D43+D44+D45</f>
+        <v>2568</v>
+      </c>
+      <c r="E46" s="41" t="n">
+        <f aca="false">E42+E43+E44+E45</f>
+        <v>2999</v>
+      </c>
+      <c r="F46" s="41" t="n">
+        <f aca="false">F42+F43+F44+F45</f>
+        <v>3568</v>
+      </c>
+      <c r="G46" s="4"/>
+    </row>
+    <row r="47" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="17"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="4"/>
+    </row>
+    <row r="48" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B48" s="40" t="n">
+        <f aca="false">B40-B46</f>
+        <v>2153</v>
+      </c>
+      <c r="C48" s="40" t="n">
+        <f aca="false">C40-C46</f>
+        <v>5144</v>
+      </c>
+      <c r="D48" s="40" t="n">
+        <f aca="false">D40-D46</f>
+        <v>7392</v>
+      </c>
+      <c r="E48" s="40" t="n">
+        <f aca="false">E40-E46</f>
+        <v>8676</v>
+      </c>
+      <c r="F48" s="40" t="n">
+        <f aca="false">F40-F46</f>
+        <v>9230</v>
+      </c>
+      <c r="G48" s="4"/>
+    </row>
+    <row r="49" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="B49" s="19" t="n">
+        <f aca="false">B24</f>
+        <v>52000</v>
+      </c>
+      <c r="C49" s="19" t="n">
+        <f aca="false">B24</f>
+        <v>52000</v>
+      </c>
+      <c r="D49" s="19" t="n">
+        <f aca="false">B24</f>
+        <v>52000</v>
+      </c>
+      <c r="E49" s="19" t="n">
+        <f aca="false">B24</f>
+        <v>52000</v>
+      </c>
+      <c r="F49" s="19" t="n">
+        <f aca="false">B24</f>
+        <v>52000</v>
+      </c>
+      <c r="G49" s="4"/>
+    </row>
+    <row r="50" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="42" t="s">
+        <v>303</v>
+      </c>
+      <c r="B50" s="43" t="n">
+        <f aca="false">B48-B49</f>
+        <v>-49847</v>
+      </c>
+      <c r="C50" s="43" t="n">
+        <f aca="false">C48-C49</f>
+        <v>-46856</v>
+      </c>
+      <c r="D50" s="43" t="n">
+        <f aca="false">D48-D49</f>
+        <v>-44608</v>
+      </c>
+      <c r="E50" s="43" t="n">
+        <f aca="false">E48-E49</f>
+        <v>-43324</v>
+      </c>
+      <c r="F50" s="43" t="n">
+        <f aca="false">F48-F49</f>
+        <v>-42770</v>
+      </c>
+      <c r="G50" s="4"/>
+    </row>
+    <row r="51" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="B51" s="30" t="n">
+        <f aca="false">IF(B40&gt;0,B50/B40,0)</f>
+        <v>-12.2383992143383</v>
+      </c>
+      <c r="C51" s="30" t="n">
+        <f aca="false">IF(C40&gt;0,C50/C40,0)</f>
+        <v>-6.36543947833175</v>
+      </c>
+      <c r="D51" s="30" t="n">
+        <f aca="false">IF(D40&gt;0,D50/D40,0)</f>
+        <v>-4.47871485943775</v>
+      </c>
+      <c r="E51" s="30" t="n">
+        <f aca="false">IF(E40&gt;0,E50/E40,0)</f>
+        <v>-3.71083511777302</v>
+      </c>
+      <c r="F51" s="30" t="n">
+        <f aca="false">IF(F40&gt;0,F50/F40,0)</f>
+        <v>-3.34192842631661</v>
+      </c>
+      <c r="G51" s="4"/>
+    </row>
+    <row r="52" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B52" s="44" t="n">
+        <f aca="false">IF(B23&gt;0,B48/(B23*52),0)</f>
+        <v>2.07019230769231</v>
+      </c>
+      <c r="C52" s="44" t="n">
+        <f aca="false">IF(B23&gt;0,C48/(B23*52),0)</f>
+        <v>4.94615384615385</v>
+      </c>
+      <c r="D52" s="44" t="n">
+        <f aca="false">IF(B23&gt;0,D48/(B23*52),0)</f>
+        <v>7.10769230769231</v>
+      </c>
+      <c r="E52" s="44" t="n">
+        <f aca="false">IF(B23&gt;0,E48/(B23*52),0)</f>
+        <v>8.34230769230769</v>
+      </c>
+      <c r="F52" s="44" t="n">
+        <f aca="false">IF(B23&gt;0,F48/(B23*52),0)</f>
+        <v>8.875</v>
+      </c>
+      <c r="G52" s="4"/>
+    </row>
+    <row r="53" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="17"/>
+      <c r="B53" s="25"/>
+      <c r="C53" s="25"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="4"/>
+    </row>
+    <row r="54" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="B54" s="39" t="n">
+        <f aca="false">B40</f>
+        <v>4073</v>
+      </c>
+      <c r="C54" s="39" t="n">
+        <f aca="false">B54+C40</f>
+        <v>11434</v>
+      </c>
+      <c r="D54" s="39" t="n">
+        <f aca="false">C54+D40</f>
+        <v>21394</v>
+      </c>
+      <c r="E54" s="39" t="n">
+        <f aca="false">D54+E40</f>
+        <v>33069</v>
+      </c>
+      <c r="F54" s="39" t="n">
+        <f aca="false">E54+F40</f>
+        <v>45867</v>
+      </c>
+      <c r="G54" s="4"/>
+    </row>
+    <row r="55" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="45" t="s">
+        <v>307</v>
+      </c>
+      <c r="B55" s="46" t="n">
+        <f aca="false">B50</f>
+        <v>-49847</v>
+      </c>
+      <c r="C55" s="46" t="n">
+        <f aca="false">B55+C50</f>
+        <v>-96703</v>
+      </c>
+      <c r="D55" s="46" t="n">
+        <f aca="false">C55+D50</f>
+        <v>-141311</v>
+      </c>
+      <c r="E55" s="46" t="n">
+        <f aca="false">D55+E50</f>
+        <v>-184635</v>
+      </c>
+      <c r="F55" s="46" t="n">
+        <f aca="false">E55+F50</f>
+        <v>-227405</v>
+      </c>
+      <c r="G55" s="4"/>
+    </row>
+    <row r="56" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+    </row>
+    <row r="57" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+    </row>
+    <row r="58" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+    </row>
+    <row r="59" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4"/>
+      <c r="B87" s="4"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4"/>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="4"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="4"/>
+      <c r="B89" s="4"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="4"/>
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A28:G28"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FFF59E0B"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D75"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="47" t="s">
+        <v>308</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="48" t="s">
+        <v>309</v>
+      </c>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="49" t="s">
+        <v>310</v>
+      </c>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+    </row>
+    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="50" t="s">
+        <v>314</v>
+      </c>
+      <c r="B6" s="51" t="s">
+        <v>315</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="45" t="s">
+        <v>318</v>
+      </c>
+      <c r="B7" s="52" t="s">
+        <v>319</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="53" t="s">
+        <v>322</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>323</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="54" t="s">
+        <v>326</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>327</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="28" t="s">
+        <v>330</v>
+      </c>
+      <c r="B10" s="51" t="s">
+        <v>331</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="55" t="s">
+        <v>333</v>
+      </c>
+      <c r="B11" s="52" t="s">
+        <v>334</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="56" t="s">
+        <v>337</v>
+      </c>
+      <c r="B12" s="51" t="s">
+        <v>338</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+    </row>
+    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="B17" s="57" t="s">
+        <v>346</v>
+      </c>
+      <c r="C17" s="57" t="s">
+        <v>346</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="B18" s="58" t="s">
+        <v>349</v>
+      </c>
+      <c r="C18" s="58" t="s">
+        <v>346</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B19" s="57" t="s">
+        <v>346</v>
+      </c>
+      <c r="C19" s="57" t="s">
+        <v>346</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="B20" s="58" t="s">
+        <v>346</v>
+      </c>
+      <c r="C20" s="58" t="s">
+        <v>346</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="B21" s="59" t="s">
+        <v>356</v>
+      </c>
+      <c r="C21" s="59" t="s">
+        <v>356</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="B22" s="60" t="s">
+        <v>356</v>
+      </c>
+      <c r="C22" s="60" t="s">
+        <v>356</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="B23" s="57" t="s">
+        <v>346</v>
+      </c>
+      <c r="C23" s="57" t="s">
+        <v>346</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="B24" s="60" t="s">
+        <v>356</v>
+      </c>
+      <c r="C24" s="58" t="s">
+        <v>346</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="B25" s="59" t="s">
+        <v>356</v>
+      </c>
+      <c r="C25" s="59" t="s">
+        <v>356</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="B26" s="60" t="s">
+        <v>356</v>
+      </c>
+      <c r="C26" s="60" t="s">
+        <v>356</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="61" t="s">
+        <v>368</v>
+      </c>
+      <c r="B29" s="61"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
+    </row>
+    <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="28" t="s">
+        <v>373</v>
+      </c>
+      <c r="B31" s="62" t="s">
+        <v>374</v>
+      </c>
+      <c r="C31" s="57" t="s">
+        <v>375</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="55" t="s">
+        <v>377</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="C32" s="60" t="s">
+        <v>356</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="C33" s="59" t="s">
+        <v>356</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="55" t="s">
+        <v>381</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="C34" s="58" t="s">
+        <v>382</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="28" t="s">
+        <v>384</v>
+      </c>
+      <c r="B35" s="63" t="s">
+        <v>356</v>
+      </c>
+      <c r="C35" s="59" t="s">
+        <v>356</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="B36" s="64" t="s">
+        <v>356</v>
+      </c>
+      <c r="C36" s="60" t="s">
+        <v>356</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="28" t="s">
+        <v>388</v>
+      </c>
+      <c r="B37" s="63" t="s">
+        <v>356</v>
+      </c>
+      <c r="C37" s="62" t="s">
+        <v>389</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="55" t="s">
+        <v>391</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="C38" s="58" t="s">
+        <v>382</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+    </row>
+    <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="65" t="s">
+        <v>393</v>
+      </c>
+      <c r="B41" s="65"/>
+      <c r="C41" s="65"/>
+      <c r="D41" s="65"/>
+    </row>
+    <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="66" t="s">
+        <v>394</v>
+      </c>
+      <c r="B42" s="66"/>
+      <c r="C42" s="66"/>
+      <c r="D42" s="66"/>
+    </row>
+    <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="66" t="s">
+        <v>395</v>
+      </c>
+      <c r="B43" s="66"/>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+    </row>
+    <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="66" t="s">
+        <v>396</v>
+      </c>
+      <c r="B44" s="66"/>
+      <c r="C44" s="66"/>
+      <c r="D44" s="66"/>
+    </row>
+    <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="66" t="s">
+        <v>397</v>
+      </c>
+      <c r="B45" s="66"/>
+      <c r="C45" s="66"/>
+      <c r="D45" s="66"/>
+    </row>
+    <row r="46" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="67"/>
+      <c r="B46" s="67"/>
+      <c r="C46" s="67"/>
+      <c r="D46" s="67"/>
+    </row>
+    <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="68" t="s">
+        <v>398</v>
+      </c>
+      <c r="B47" s="68"/>
+      <c r="C47" s="68"/>
+      <c r="D47" s="68"/>
+    </row>
+    <row r="48" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="67"/>
+      <c r="B48" s="67"/>
+      <c r="C48" s="67"/>
+      <c r="D48" s="67"/>
+    </row>
+    <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="69" t="s">
+        <v>399</v>
+      </c>
+      <c r="B49" s="69"/>
+      <c r="C49" s="69"/>
+      <c r="D49" s="69"/>
+    </row>
+    <row r="50" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="67"/>
+      <c r="B50" s="67"/>
+      <c r="C50" s="67"/>
+      <c r="D50" s="67"/>
+    </row>
+    <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="70" t="s">
+        <v>400</v>
+      </c>
+      <c r="B51" s="70"/>
+      <c r="C51" s="70"/>
+      <c r="D51" s="70"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A51:D51"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>